--- a/internal_doc/05.测试设计/sdv/2.0版本SDV测试策略.xlsx
+++ b/internal_doc/05.测试设计/sdv/2.0版本SDV测试策略.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="-300" windowWidth="17715" windowHeight="8010"/>
+    <workbookView xWindow="1440" yWindow="-300" windowWidth="17715" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="特性" sheetId="4" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="152">
   <si>
     <t>aggregate</t>
   </si>
@@ -640,6 +640,10 @@
   </si>
   <si>
     <t>测试结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ok</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1934,7 +1938,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:4">
       <c r="A33" t="s">
         <v>80</v>
       </c>
@@ -1945,22 +1949,22 @@
         <v>145</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:4">
       <c r="B34" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:4">
       <c r="B35" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:4">
       <c r="B36" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:4">
       <c r="A37" t="s">
         <v>81</v>
       </c>
@@ -1970,48 +1974,75 @@
       <c r="C37" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="38" spans="1:3">
+      <c r="D37" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
       <c r="B38" s="25" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="39" spans="1:3">
+      <c r="D38" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
       <c r="B39" s="25" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="40" spans="1:3">
+      <c r="D39" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
       <c r="B40" s="25" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="41" spans="1:3">
+      <c r="D40" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
       <c r="B41" s="25" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="42" spans="1:3">
+      <c r="D41" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
       <c r="B42" s="25" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="43" spans="1:3">
+      <c r="D42" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
       <c r="B43" s="25" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="44" spans="1:3">
+      <c r="D43" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
       <c r="B44" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="45" spans="1:3">
+      <c r="D44" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
       <c r="B45" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="46" spans="1:3">
+      <c r="D45" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
       <c r="A46" t="s">
         <v>82</v>
       </c>
@@ -2022,15 +2053,18 @@
         <v>144</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:4">
       <c r="B47" s="23" t="s">
         <v>102</v>
       </c>
       <c r="C47" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="48" spans="1:3">
+      <c r="D47" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
       <c r="B48" s="25" t="s">
         <v>103</v>
       </c>
@@ -2038,32 +2072,32 @@
         <v>145</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:4">
       <c r="B49" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:4">
       <c r="B50" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:4">
       <c r="B51" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:4">
       <c r="B52" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:4">
       <c r="A53" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:4">
       <c r="A54" t="s">
         <v>109</v>
       </c>
@@ -2073,38 +2107,56 @@
       <c r="C54" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="55" spans="1:3">
+      <c r="D54" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
       <c r="B55" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="56" spans="1:3">
+      <c r="D55" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
       <c r="B56" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="57" spans="1:3">
+      <c r="D56" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
       <c r="B57" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="58" spans="1:3">
+      <c r="D57" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
       <c r="B58" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="59" spans="1:3">
+      <c r="D58" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
       <c r="B59" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="61" spans="1:3">
+      <c r="D59" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
       <c r="A61" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:4">
       <c r="A62" t="s">
         <v>148</v>
       </c>

--- a/internal_doc/05.测试设计/sdv/2.0版本SDV测试策略.xlsx
+++ b/internal_doc/05.测试设计/sdv/2.0版本SDV测试策略.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="153">
   <si>
     <t>aggregate</t>
   </si>
@@ -644,6 +644,10 @@
   </si>
   <si>
     <t>ok</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>failed</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -846,74 +850,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -925,7 +861,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CCE8CF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -1763,31 +1699,49 @@
       <c r="C2" t="s">
         <v>145</v>
       </c>
+      <c r="D2" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="3" spans="1:4">
       <c r="B3" s="25" t="s">
         <v>117</v>
       </c>
+      <c r="D3" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="4" spans="1:4">
       <c r="B4" t="s">
         <v>118</v>
       </c>
+      <c r="D4" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="5" spans="1:4">
       <c r="B5" t="s">
         <v>119</v>
       </c>
+      <c r="D5" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="6" spans="1:4">
       <c r="B6" t="s">
         <v>120</v>
       </c>
+      <c r="D6" s="23" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="7" spans="1:4">
       <c r="B7" t="s">
         <v>121</v>
       </c>
+      <c r="D7" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
@@ -1846,12 +1800,12 @@
         <v>128</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:4">
       <c r="B17" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
         <v>78</v>
       </c>
@@ -1861,38 +1815,59 @@
       <c r="C18" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="D18" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="B19" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="B20" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="D20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="B21" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
+      <c r="D21" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
       <c r="B22" s="25" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
+      <c r="D22" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
       <c r="B23" s="24" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
+      <c r="D23" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
       <c r="B24" s="24" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
+      <c r="D24" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25" t="s">
         <v>79</v>
       </c>
@@ -1902,40 +1877,64 @@
       <c r="C25" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
+      <c r="D25" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
       <c r="B26" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
+      <c r="D26" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
       <c r="B27" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="28" spans="1:3">
+      <c r="D27" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
       <c r="B28" s="25" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="29" spans="1:3">
+      <c r="D28" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
       <c r="B29" s="25" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="30" spans="1:3">
+      <c r="D29" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
       <c r="B30" s="25" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="31" spans="1:3">
+      <c r="D30" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
       <c r="B31" s="25" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="32" spans="1:3">
+      <c r="D31" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
       <c r="B32" s="25" t="s">
         <v>90</v>
+      </c>
+      <c r="D32" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1948,21 +1947,33 @@
       <c r="C33" t="s">
         <v>145</v>
       </c>
+      <c r="D33" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="34" spans="1:4">
       <c r="B34" t="s">
         <v>92</v>
       </c>
+      <c r="D34" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="35" spans="1:4">
       <c r="B35" t="s">
         <v>93</v>
       </c>
+      <c r="D35" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="36" spans="1:4">
       <c r="B36" t="s">
         <v>94</v>
       </c>
+      <c r="D36" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
@@ -2071,30 +2082,48 @@
       <c r="C48" t="s">
         <v>145</v>
       </c>
+      <c r="D48" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="49" spans="1:4">
       <c r="B49" t="s">
         <v>104</v>
       </c>
+      <c r="D49" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="50" spans="1:4">
       <c r="B50" t="s">
         <v>105</v>
       </c>
+      <c r="D50" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="51" spans="1:4">
       <c r="B51" t="s">
         <v>106</v>
       </c>
+      <c r="D51" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="52" spans="1:4">
       <c r="B52" t="s">
         <v>107</v>
       </c>
+      <c r="D52" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
         <v>108</v>
+      </c>
+      <c r="D53" s="23" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="54" spans="1:4">

--- a/internal_doc/05.测试设计/sdv/2.0版本SDV测试策略.xlsx
+++ b/internal_doc/05.测试设计/sdv/2.0版本SDV测试策略.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="154">
   <si>
     <t>aggregate</t>
   </si>
@@ -648,6 +648,10 @@
   </si>
   <si>
     <t>failed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已提单</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1669,13 +1673,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="23.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>74</v>
       </c>
@@ -1689,7 +1693,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>75</v>
       </c>
@@ -1703,7 +1707,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5">
       <c r="B3" s="25" t="s">
         <v>117</v>
       </c>
@@ -1711,7 +1715,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:5">
       <c r="B4" t="s">
         <v>118</v>
       </c>
@@ -1719,7 +1723,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5">
       <c r="B5" t="s">
         <v>119</v>
       </c>
@@ -1727,15 +1731,18 @@
         <v>151</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:5">
       <c r="B6" t="s">
         <v>120</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="B7" t="s">
         <v>121</v>
       </c>
@@ -1743,7 +1750,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>76</v>
       </c>
@@ -1753,28 +1760,46 @@
       <c r="C8" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="D8" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="B9" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="D9" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="E9" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="B10" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="D10" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="B11" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="D11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="B12" s="25" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="D12" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>77</v>
       </c>
@@ -1784,26 +1809,41 @@
       <c r="C13" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="D13" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="B14" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="D14" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="B15" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="D15" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="B16" t="s">
         <v>128</v>
+      </c>
+      <c r="D16" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="B17" t="s">
         <v>129</v>
       </c>
+      <c r="D17" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
@@ -2063,6 +2103,9 @@
       <c r="C46" t="s">
         <v>144</v>
       </c>
+      <c r="D46" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="47" spans="1:4">
       <c r="B47" s="23" t="s">
@@ -2086,7 +2129,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:5">
       <c r="B49" t="s">
         <v>104</v>
       </c>
@@ -2094,7 +2137,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:5">
       <c r="B50" t="s">
         <v>105</v>
       </c>
@@ -2102,7 +2145,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:5">
       <c r="B51" t="s">
         <v>106</v>
       </c>
@@ -2110,7 +2153,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:5">
       <c r="B52" t="s">
         <v>107</v>
       </c>
@@ -2118,15 +2161,18 @@
         <v>151</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:5">
       <c r="A53" t="s">
         <v>108</v>
       </c>
       <c r="D53" s="23" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="54" spans="1:4">
+      <c r="E53" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
       <c r="A54" t="s">
         <v>109</v>
       </c>
@@ -2140,7 +2186,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:5">
       <c r="B55" t="s">
         <v>111</v>
       </c>
@@ -2148,7 +2194,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:5">
       <c r="B56" t="s">
         <v>112</v>
       </c>
@@ -2156,7 +2202,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:5">
       <c r="B57" t="s">
         <v>113</v>
       </c>
@@ -2164,7 +2210,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:5">
       <c r="B58" t="s">
         <v>114</v>
       </c>
@@ -2172,7 +2218,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:5">
       <c r="B59" t="s">
         <v>115</v>
       </c>
@@ -2180,12 +2226,12 @@
         <v>151</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:5">
       <c r="A61" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
+    <row r="62" spans="1:5">
       <c r="A62" t="s">
         <v>148</v>
       </c>
